--- a/public/ValueSet-observation-scored-assessment-score-codes.xlsx
+++ b/public/ValueSet-observation-scored-assessment-score-codes.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:28:41-06:00</t>
+    <t>2026-09-10T16:32:51-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/ValueSet-observation-scored-assessment-score-codes.xlsx
+++ b/public/ValueSet-observation-scored-assessment-score-codes.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Observation State of Mind Codes</t>
+    <t>Scored Assessment Score Value Set</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-20T16:07:18-05:00</t>
+    <t>2026-10-08T19:53:09-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Codes for state of mind</t>
+    <t>Codes for scored assessment scores (e.g. GAD-7, PHQ-9)</t>
   </si>
   <si>
     <t>Purpose</t>
